--- a/docs/PPG/Blogs externos.xlsx
+++ b/docs/PPG/Blogs externos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arthurferreira/Google Drive - arthur_sf/Observatorios/ObservatorioUNISUAM-CR/PPG/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0324625-A415-174A-BF2A-1EA91D400F34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99D68FF7-70CF-E244-9D5B-C494E26B878B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1060" yWindow="680" windowWidth="27500" windowHeight="16900" xr2:uid="{532D0FCC-2B74-AC48-A173-8BCE0F3E070A}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="110">
   <si>
     <t>Publicação</t>
   </si>
@@ -357,6 +357,15 @@
   </si>
   <si>
     <t>https://www.hsu.ac.uk/hsu-innovation-chosen-for-global-who-showcase-on-traditional-medicine/</t>
+  </si>
+  <si>
+    <t>2026</t>
+  </si>
+  <si>
+    <t>https://www.crefito2.gov.br/home_profissional/conteudo/crefito2_marca_presenca_no_futsummit_26_e_reforca_protagonismo_da_fisioterapia_e_terapia_ocupacional_no_esporte_7563</t>
+  </si>
+  <si>
+    <t>Crefito-2 marca presença no FutSummit 26 e reforça protagonismo da Fisioterapia e Terapia Ocupacional no esporte</t>
   </si>
 </sst>
 </file>
@@ -729,7 +738,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9C7B3C5-88EC-8F41-9FD9-49FAABD7FF8A}">
-  <dimension ref="A1:D45"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.33203125" style="2" bestFit="1" customWidth="1"/>
@@ -1367,6 +1376,20 @@
       </c>
       <c r="D45" s="3" t="s">
         <v>106</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A46" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -1418,6 +1441,7 @@
     <hyperlink ref="D43" r:id="rId41" xr:uid="{1EF918EE-6765-A345-B3FB-956B76B81A79}"/>
     <hyperlink ref="D44" r:id="rId42" xr:uid="{019A228A-E4F1-B14D-B36B-EB7979E5AFD5}"/>
     <hyperlink ref="D45" r:id="rId43" xr:uid="{B619F7DE-B7AA-1D42-866A-2A495D8AB900}"/>
+    <hyperlink ref="D46" r:id="rId44" xr:uid="{032C6291-2082-3748-B914-64768DCDB5C0}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/docs/PPG/Blogs externos.xlsx
+++ b/docs/PPG/Blogs externos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arthurferreira/Google Drive - arthur_sf/Observatorios/ObservatorioUNISUAM-CR/PPG/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99D68FF7-70CF-E244-9D5B-C494E26B878B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97FCB3F7-A66D-7049-9826-F90576ACFAB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1060" yWindow="680" windowWidth="27500" windowHeight="16900" xr2:uid="{532D0FCC-2B74-AC48-A173-8BCE0F3E070A}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="120">
   <si>
     <t>Publicação</t>
   </si>
@@ -366,6 +366,36 @@
   </si>
   <si>
     <t>Crefito-2 marca presença no FutSummit 26 e reforça protagonismo da Fisioterapia e Terapia Ocupacional no esporte</t>
+  </si>
+  <si>
+    <t>https://unilavras.edu.br/2026/04/13/pesquisadora-do-unilavras-publica-artigo-na-maior-revista-de-fisioterapia-do-mundo/</t>
+  </si>
+  <si>
+    <t>PESQUISADORA DO UNILAVRAS PUBLICA ARTIGO NA MAIOR REVISTA DE FISIOTERAPIA DO MUNDO</t>
+  </si>
+  <si>
+    <t>Pesquisadora do Unilavras publica artigo na maior revista de Fisioterapia do mundo</t>
+  </si>
+  <si>
+    <t>https://www.jornaldelavras.com.br/index.php?p=10&amp;tc=4&amp;c=38124&amp;utm_source=ig&amp;utm_medium=social&amp;utm_content=link_in_bio</t>
+  </si>
+  <si>
+    <t>https://lavras.tv/site/2026/04/13/pesquisadora-do-unilavras-publica-artigo-na-maior-revista-de-fisioterapia-do-mundo/?utm_source=ig&amp;utm_medium=social&amp;utm_content=link_in_bio</t>
+  </si>
+  <si>
+    <t>https://tribunadepetropolis.com.br/noticias/professor-petropolitano-se-destaca-internacionalmente-com-pesquisas-em-saude-do-musico/</t>
+  </si>
+  <si>
+    <t>Áustria</t>
+  </si>
+  <si>
+    <t>Professor petropolitano se destaca internacionalmente com pesquisas em saúde do músico</t>
+  </si>
+  <si>
+    <t>Dores e cansaço são sinais de alerta para fibromialgia e síndrome da fadiga crônica</t>
+  </si>
+  <si>
+    <t>https://www.gov.br/hubrasil/pt-br/hospitais-universitarios/regiao-sudeste/huap-uff/comunicacao/noticias/dores-e-cansaco-sao-sinais-de-alerta-para-fibromialgia-e-sindrome-da-fadiga-cronica</t>
   </si>
 </sst>
 </file>
@@ -738,7 +768,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9C7B3C5-88EC-8F41-9FD9-49FAABD7FF8A}">
-  <dimension ref="A1:D46"/>
+  <dimension ref="A1:D51"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.33203125" style="2" bestFit="1" customWidth="1"/>
@@ -1390,6 +1420,76 @@
       </c>
       <c r="D46" s="3" t="s">
         <v>108</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A47" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A48" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A49" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A50" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A51" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -1442,6 +1542,11 @@
     <hyperlink ref="D44" r:id="rId42" xr:uid="{019A228A-E4F1-B14D-B36B-EB7979E5AFD5}"/>
     <hyperlink ref="D45" r:id="rId43" xr:uid="{B619F7DE-B7AA-1D42-866A-2A495D8AB900}"/>
     <hyperlink ref="D46" r:id="rId44" xr:uid="{032C6291-2082-3748-B914-64768DCDB5C0}"/>
+    <hyperlink ref="D47" r:id="rId45" xr:uid="{29F13EA1-9D36-D84D-B5D0-97965A7F6B08}"/>
+    <hyperlink ref="D48" r:id="rId46" xr:uid="{A42C8BDD-B3F4-B44F-A8A3-6E254B43BEDE}"/>
+    <hyperlink ref="D49" r:id="rId47" xr:uid="{E6CB8715-3697-3041-8411-F7A291F77306}"/>
+    <hyperlink ref="D50" r:id="rId48" xr:uid="{C54AAE11-E5B4-C947-9FAC-5B7A995F2C11}"/>
+    <hyperlink ref="D51" r:id="rId49" xr:uid="{91008C25-8C52-5042-B50B-35E16CD70CC8}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
